--- a/meter_rank_old.xlsx
+++ b/meter_rank_old.xlsx
@@ -486,29 +486,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ol-plg</t>
+          <t>liq-olpyxspplgsat</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>497</v>
+        <v>2256</v>
       </c>
       <c r="D2" t="n">
-        <v>0.447</v>
+        <v>0.671</v>
       </c>
       <c r="E2" t="n">
-        <v>1.176</v>
+        <v>1.761</v>
       </c>
       <c r="F2" t="n">
-        <v>15.231</v>
+        <v>18.527</v>
       </c>
       <c r="G2" t="n">
-        <v>39.74</v>
+        <v>48.71</v>
       </c>
       <c r="H2" t="n">
-        <v>0.868</v>
+        <v>1.3</v>
       </c>
       <c r="I2" t="n">
-        <v>2.275</v>
+        <v>3.401</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -522,29 +522,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>liq-plg</t>
+          <t>liq-pyxspplgsat</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>775</v>
+        <v>1226</v>
       </c>
       <c r="D3" t="n">
-        <v>0.442</v>
+        <v>0.588</v>
       </c>
       <c r="E3" t="n">
-        <v>1.185</v>
+        <v>1.539</v>
       </c>
       <c r="F3" t="n">
-        <v>11.184</v>
+        <v>15.658</v>
       </c>
       <c r="G3" t="n">
-        <v>28.745</v>
+        <v>41.095</v>
       </c>
       <c r="H3" t="n">
-        <v>0.833</v>
+        <v>1.118</v>
       </c>
       <c r="I3" t="n">
-        <v>2.206</v>
+        <v>2.952</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -558,29 +558,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>liq-ol</t>
+          <t>liq-plgsat</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>765</v>
+        <v>1020</v>
       </c>
       <c r="D4" t="n">
-        <v>0.488</v>
+        <v>0.513</v>
       </c>
       <c r="E4" t="n">
-        <v>1.255</v>
+        <v>1.332</v>
       </c>
       <c r="F4" t="n">
-        <v>14.18</v>
+        <v>12.871</v>
       </c>
       <c r="G4" t="n">
-        <v>37.107</v>
+        <v>34.149</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9340000000000001</v>
+        <v>1.011</v>
       </c>
       <c r="I4" t="n">
-        <v>2.457</v>
+        <v>2.662</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -594,29 +594,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>liq-plgsat</t>
+          <t>ol</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1020</v>
+        <v>776</v>
       </c>
       <c r="D5" t="n">
-        <v>0.513</v>
+        <v>0.661</v>
       </c>
       <c r="E5" t="n">
-        <v>1.332</v>
+        <v>1.752</v>
       </c>
       <c r="F5" t="n">
-        <v>12.871</v>
+        <v>22.348</v>
       </c>
       <c r="G5" t="n">
-        <v>34.149</v>
+        <v>59.266</v>
       </c>
       <c r="H5" t="n">
-        <v>1.011</v>
+        <v>1.204</v>
       </c>
       <c r="I5" t="n">
-        <v>2.662</v>
+        <v>3.223</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -630,29 +630,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>liq-cpx</t>
+          <t>cpx</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>751</v>
+        <v>766</v>
       </c>
       <c r="D6" t="n">
-        <v>0.547</v>
+        <v>0.713</v>
       </c>
       <c r="E6" t="n">
-        <v>1.434</v>
+        <v>1.858</v>
       </c>
       <c r="F6" t="n">
-        <v>12.996</v>
+        <v>20.261</v>
       </c>
       <c r="G6" t="n">
-        <v>34.411</v>
+        <v>53.728</v>
       </c>
       <c r="H6" t="n">
-        <v>0.799</v>
+        <v>0.828</v>
       </c>
       <c r="I6" t="n">
-        <v>2.084</v>
+        <v>2.247</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -666,29 +666,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ol-cpx</t>
+          <t>plg</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>487</v>
+        <v>778</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.745</v>
       </c>
       <c r="E7" t="n">
-        <v>1.489</v>
+        <v>1.985</v>
       </c>
       <c r="F7" t="n">
-        <v>16.207</v>
+        <v>26.442</v>
       </c>
       <c r="G7" t="n">
-        <v>42.471</v>
+        <v>70.504</v>
       </c>
       <c r="H7" t="n">
-        <v>0.792</v>
+        <v>1.07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.069</v>
+        <v>2.815</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -702,29 +702,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>cpx-plg</t>
+          <t>opx</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>537</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>0.573</v>
+        <v>0.765</v>
       </c>
       <c r="E8" t="n">
-        <v>1.526</v>
+        <v>2.007</v>
       </c>
       <c r="F8" t="n">
-        <v>17.857</v>
+        <v>23.414</v>
       </c>
       <c r="G8" t="n">
-        <v>46.832</v>
+        <v>60.947</v>
       </c>
       <c r="H8" t="n">
-        <v>0.605</v>
+        <v>0.885</v>
       </c>
       <c r="I8" t="n">
-        <v>1.611</v>
+        <v>2.261</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -738,29 +738,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>liq-pyxspplgsat</t>
+          <t>liq-ol</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1226</v>
+        <v>765</v>
       </c>
       <c r="D9" t="n">
-        <v>0.588</v>
+        <v>0.488</v>
       </c>
       <c r="E9" t="n">
-        <v>1.539</v>
+        <v>1.255</v>
       </c>
       <c r="F9" t="n">
-        <v>15.658</v>
+        <v>14.18</v>
       </c>
       <c r="G9" t="n">
-        <v>41.095</v>
+        <v>37.107</v>
       </c>
       <c r="H9" t="n">
-        <v>1.118</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>2.952</v>
+        <v>2.457</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -774,29 +774,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>liq-opx</t>
+          <t>liq-cpx</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>284</v>
+        <v>751</v>
       </c>
       <c r="D10" t="n">
-        <v>0.619</v>
+        <v>0.547</v>
       </c>
       <c r="E10" t="n">
-        <v>1.626</v>
+        <v>1.434</v>
       </c>
       <c r="F10" t="n">
-        <v>15.73</v>
+        <v>12.996</v>
       </c>
       <c r="G10" t="n">
-        <v>40.592</v>
+        <v>34.411</v>
       </c>
       <c r="H10" t="n">
-        <v>0.794</v>
+        <v>0.799</v>
       </c>
       <c r="I10" t="n">
-        <v>2.009</v>
+        <v>2.084</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -810,29 +810,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>liq-sp</t>
+          <t>liq-plg</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>206</v>
+        <v>775</v>
       </c>
       <c r="D11" t="n">
-        <v>0.672</v>
+        <v>0.442</v>
       </c>
       <c r="E11" t="n">
-        <v>1.638</v>
+        <v>1.185</v>
       </c>
       <c r="F11" t="n">
-        <v>19.241</v>
+        <v>11.184</v>
       </c>
       <c r="G11" t="n">
-        <v>50.078</v>
+        <v>28.745</v>
       </c>
       <c r="H11" t="n">
-        <v>1.091</v>
+        <v>0.833</v>
       </c>
       <c r="I11" t="n">
-        <v>2.833</v>
+        <v>2.206</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -846,29 +846,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ol</t>
+          <t>liq-opx</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>776</v>
+        <v>284</v>
       </c>
       <c r="D12" t="n">
-        <v>0.661</v>
+        <v>0.619</v>
       </c>
       <c r="E12" t="n">
-        <v>1.752</v>
+        <v>1.626</v>
       </c>
       <c r="F12" t="n">
-        <v>22.348</v>
+        <v>15.73</v>
       </c>
       <c r="G12" t="n">
-        <v>59.266</v>
+        <v>40.592</v>
       </c>
       <c r="H12" t="n">
-        <v>1.204</v>
+        <v>0.794</v>
       </c>
       <c r="I12" t="n">
-        <v>3.223</v>
+        <v>2.009</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -882,29 +882,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>liq-olpyxspplgsat</t>
+          <t>ol-cpx</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2256</v>
+        <v>487</v>
       </c>
       <c r="D13" t="n">
-        <v>0.671</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>1.761</v>
+        <v>1.489</v>
       </c>
       <c r="F13" t="n">
-        <v>18.527</v>
+        <v>16.207</v>
       </c>
       <c r="G13" t="n">
-        <v>48.71</v>
+        <v>42.471</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3</v>
+        <v>0.792</v>
       </c>
       <c r="I13" t="n">
-        <v>3.401</v>
+        <v>2.069</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -918,29 +918,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>cpx-opx</t>
+          <t>ol-plg</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>215</v>
+        <v>497</v>
       </c>
       <c r="D14" t="n">
-        <v>0.709</v>
+        <v>0.447</v>
       </c>
       <c r="E14" t="n">
-        <v>1.843</v>
+        <v>1.176</v>
       </c>
       <c r="F14" t="n">
-        <v>20.283</v>
+        <v>15.231</v>
       </c>
       <c r="G14" t="n">
-        <v>52.261</v>
+        <v>39.74</v>
       </c>
       <c r="H14" t="n">
-        <v>0.835</v>
+        <v>0.868</v>
       </c>
       <c r="I14" t="n">
-        <v>2.111</v>
+        <v>2.275</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -954,29 +954,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>cpx</t>
+          <t>cpx-plg</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>766</v>
+        <v>537</v>
       </c>
       <c r="D15" t="n">
-        <v>0.713</v>
+        <v>0.573</v>
       </c>
       <c r="E15" t="n">
-        <v>1.858</v>
+        <v>1.526</v>
       </c>
       <c r="F15" t="n">
-        <v>20.261</v>
+        <v>17.857</v>
       </c>
       <c r="G15" t="n">
-        <v>53.728</v>
+        <v>46.832</v>
       </c>
       <c r="H15" t="n">
-        <v>0.828</v>
+        <v>0.605</v>
       </c>
       <c r="I15" t="n">
-        <v>2.247</v>
+        <v>1.611</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -985,160 +985,168 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>cpx-opx</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>215</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.843</v>
+      </c>
+      <c r="F17" t="n">
+        <v>20.283</v>
+      </c>
+      <c r="G17" t="n">
+        <v>52.261</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.111</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>plg-opx</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C18" t="n">
         <v>208</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D18" t="n">
         <v>0.721</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E18" t="n">
         <v>1.94</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F18" t="n">
         <v>24.794</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G18" t="n">
         <v>65.69199999999999</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H18" t="n">
         <v>0.799</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I18" t="n">
         <v>1.997</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>plg</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>778</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1.985</v>
-      </c>
-      <c r="F17" t="n">
-        <v>26.442</v>
-      </c>
-      <c r="G17" t="n">
-        <v>70.504</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2.815</v>
-      </c>
-      <c r="J17" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>liq-sp</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>206</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.638</v>
+      </c>
+      <c r="F19" t="n">
+        <v>19.241</v>
+      </c>
+      <c r="G19" t="n">
+        <v>50.078</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.091</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.833</v>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>opx</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>287</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2.007</v>
-      </c>
-      <c r="F18" t="n">
-        <v>23.414</v>
-      </c>
-      <c r="G18" t="n">
-        <v>60.947</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.261</v>
-      </c>
-      <c r="J18" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>sp</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>205</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="F20" t="n">
+        <v>22.979</v>
+      </c>
+      <c r="G20" t="n">
+        <v>60.449</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.942</v>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>sp</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>205</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2.138</v>
-      </c>
-      <c r="F19" t="n">
-        <v>22.979</v>
-      </c>
-      <c r="G19" t="n">
-        <v>60.449</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.139</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2.942</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1556,29 +1564,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>liq-ilm</t>
+          <t>ilm</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>74</v>
       </c>
       <c r="D33" t="n">
-        <v>0.771</v>
+        <v>1.081</v>
       </c>
       <c r="E33" t="n">
-        <v>1.996</v>
+        <v>2.883</v>
       </c>
       <c r="F33" t="n">
-        <v>10.945</v>
+        <v>28.393</v>
       </c>
       <c r="G33" t="n">
-        <v>28.63</v>
+        <v>74.161</v>
       </c>
       <c r="H33" t="n">
-        <v>0.833</v>
+        <v>0.857</v>
       </c>
       <c r="I33" t="n">
-        <v>2.219</v>
+        <v>2.285</v>
       </c>
       <c r="J33" t="inlineStr"/>
     </row>
@@ -1590,29 +1598,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ilm</t>
+          <t>liq-ilm</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>74</v>
       </c>
       <c r="D34" t="n">
-        <v>1.081</v>
+        <v>0.771</v>
       </c>
       <c r="E34" t="n">
-        <v>2.883</v>
+        <v>1.996</v>
       </c>
       <c r="F34" t="n">
-        <v>28.393</v>
+        <v>10.945</v>
       </c>
       <c r="G34" t="n">
-        <v>74.161</v>
+        <v>28.63</v>
       </c>
       <c r="H34" t="n">
-        <v>0.857</v>
+        <v>0.833</v>
       </c>
       <c r="I34" t="n">
-        <v>2.285</v>
+        <v>2.219</v>
       </c>
       <c r="J34" t="inlineStr"/>
     </row>
@@ -1692,29 +1700,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>opx-mag</t>
+          <t>ol-mag</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>66</v>
       </c>
       <c r="D37" t="n">
-        <v>0.755</v>
+        <v>0.465</v>
       </c>
       <c r="E37" t="n">
-        <v>1.983</v>
+        <v>1.187</v>
       </c>
       <c r="F37" t="n">
-        <v>18.617</v>
+        <v>12.841</v>
       </c>
       <c r="G37" t="n">
-        <v>45.956</v>
+        <v>33.587</v>
       </c>
       <c r="H37" t="n">
-        <v>0.621</v>
+        <v>1.126</v>
       </c>
       <c r="I37" t="n">
-        <v>1.601</v>
+        <v>2.802</v>
       </c>
       <c r="J37" t="inlineStr"/>
     </row>
@@ -1726,29 +1734,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ol-mag</t>
+          <t>opx-mag</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>66</v>
       </c>
       <c r="D38" t="n">
-        <v>0.465</v>
+        <v>0.755</v>
       </c>
       <c r="E38" t="n">
-        <v>1.187</v>
+        <v>1.983</v>
       </c>
       <c r="F38" t="n">
-        <v>12.841</v>
+        <v>18.617</v>
       </c>
       <c r="G38" t="n">
-        <v>33.587</v>
+        <v>45.956</v>
       </c>
       <c r="H38" t="n">
-        <v>1.126</v>
+        <v>0.621</v>
       </c>
       <c r="I38" t="n">
-        <v>2.802</v>
+        <v>1.601</v>
       </c>
       <c r="J38" t="inlineStr"/>
     </row>
@@ -1862,29 +1870,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>liq-grt</t>
+          <t>grt</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>43</v>
       </c>
       <c r="D42" t="n">
-        <v>0.906</v>
+        <v>0.973</v>
       </c>
       <c r="E42" t="n">
-        <v>2.29</v>
+        <v>2.384</v>
       </c>
       <c r="F42" t="n">
-        <v>22.765</v>
+        <v>28.818</v>
       </c>
       <c r="G42" t="n">
-        <v>56.793</v>
+        <v>68.611</v>
       </c>
       <c r="H42" t="n">
-        <v>0.897</v>
+        <v>0.876</v>
       </c>
       <c r="I42" t="n">
-        <v>2.329</v>
+        <v>2.11</v>
       </c>
       <c r="J42" t="inlineStr"/>
     </row>
@@ -1896,29 +1904,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>grt</t>
+          <t>liq-grt</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>43</v>
       </c>
       <c r="D43" t="n">
-        <v>0.973</v>
+        <v>0.906</v>
       </c>
       <c r="E43" t="n">
-        <v>2.384</v>
+        <v>2.29</v>
       </c>
       <c r="F43" t="n">
-        <v>28.818</v>
+        <v>22.765</v>
       </c>
       <c r="G43" t="n">
-        <v>68.611</v>
+        <v>56.793</v>
       </c>
       <c r="H43" t="n">
-        <v>0.876</v>
+        <v>0.897</v>
       </c>
       <c r="I43" t="n">
-        <v>2.11</v>
+        <v>2.329</v>
       </c>
       <c r="J43" t="inlineStr"/>
     </row>
@@ -1930,29 +1938,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ol-amph</t>
+          <t>amph-ilm</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>36</v>
       </c>
       <c r="D44" t="n">
-        <v>0.627</v>
+        <v>0.618</v>
       </c>
       <c r="E44" t="n">
-        <v>1.476</v>
+        <v>1.652</v>
       </c>
       <c r="F44" t="n">
-        <v>11.148</v>
+        <v>11.255</v>
       </c>
       <c r="G44" t="n">
-        <v>28.488</v>
+        <v>28.259</v>
       </c>
       <c r="H44" t="n">
-        <v>0.721</v>
+        <v>0.596</v>
       </c>
       <c r="I44" t="n">
-        <v>1.652</v>
+        <v>1.408</v>
       </c>
       <c r="J44" t="inlineStr"/>
     </row>
@@ -1964,29 +1972,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>amph-ilm</t>
+          <t>ol-amph</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>36</v>
       </c>
       <c r="D45" t="n">
-        <v>0.618</v>
+        <v>0.627</v>
       </c>
       <c r="E45" t="n">
+        <v>1.476</v>
+      </c>
+      <c r="F45" t="n">
+        <v>11.148</v>
+      </c>
+      <c r="G45" t="n">
+        <v>28.488</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="I45" t="n">
         <v>1.652</v>
-      </c>
-      <c r="F45" t="n">
-        <v>11.255</v>
-      </c>
-      <c r="G45" t="n">
-        <v>28.259</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.596</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1.408</v>
       </c>
       <c r="J45" t="inlineStr"/>
     </row>

--- a/meter_rank_old.xlsx
+++ b/meter_rank_old.xlsx
@@ -1004,35 +1004,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>cpx-opx</t>
+          <t>amph</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>215</v>
+        <v>157</v>
       </c>
       <c r="D17" t="n">
-        <v>0.709</v>
+        <v>0.617</v>
       </c>
       <c r="E17" t="n">
-        <v>1.843</v>
+        <v>1.639</v>
       </c>
       <c r="F17" t="n">
-        <v>20.283</v>
+        <v>12.722</v>
       </c>
       <c r="G17" t="n">
-        <v>52.261</v>
+        <v>32.804</v>
       </c>
       <c r="H17" t="n">
-        <v>0.835</v>
+        <v>0.699</v>
       </c>
       <c r="I17" t="n">
-        <v>2.111</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+        <v>1.838</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1042,35 +1038,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>plg-opx</t>
+          <t>ilm</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>208</v>
+        <v>74</v>
       </c>
       <c r="D18" t="n">
-        <v>0.721</v>
+        <v>1.081</v>
       </c>
       <c r="E18" t="n">
-        <v>1.94</v>
+        <v>2.883</v>
       </c>
       <c r="F18" t="n">
-        <v>24.794</v>
+        <v>28.393</v>
       </c>
       <c r="G18" t="n">
-        <v>65.69199999999999</v>
+        <v>74.161</v>
       </c>
       <c r="H18" t="n">
-        <v>0.799</v>
+        <v>0.857</v>
       </c>
       <c r="I18" t="n">
-        <v>1.997</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+        <v>2.285</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1080,35 +1072,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>liq-sp</t>
+          <t>mag</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>206</v>
+        <v>157</v>
       </c>
       <c r="D19" t="n">
-        <v>0.672</v>
+        <v>0.737</v>
       </c>
       <c r="E19" t="n">
-        <v>1.638</v>
+        <v>1.947</v>
       </c>
       <c r="F19" t="n">
-        <v>19.241</v>
+        <v>18.81</v>
       </c>
       <c r="G19" t="n">
-        <v>50.078</v>
+        <v>46.507</v>
       </c>
       <c r="H19" t="n">
-        <v>1.091</v>
+        <v>1.113</v>
       </c>
       <c r="I19" t="n">
-        <v>2.833</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+        <v>3.002</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1156,29 +1144,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>amph</t>
+          <t>grt</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>157</v>
+        <v>43</v>
       </c>
       <c r="D21" t="n">
-        <v>0.617</v>
+        <v>0.973</v>
       </c>
       <c r="E21" t="n">
-        <v>1.639</v>
+        <v>2.384</v>
       </c>
       <c r="F21" t="n">
-        <v>12.722</v>
+        <v>28.818</v>
       </c>
       <c r="G21" t="n">
-        <v>32.804</v>
+        <v>68.611</v>
       </c>
       <c r="H21" t="n">
-        <v>0.699</v>
+        <v>0.876</v>
       </c>
       <c r="I21" t="n">
-        <v>1.838</v>
+        <v>2.11</v>
       </c>
       <c r="J21" t="inlineStr"/>
     </row>
@@ -1190,29 +1178,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>mag</t>
+          <t>liq-amph</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>157</v>
       </c>
       <c r="D22" t="n">
-        <v>0.737</v>
+        <v>0.592</v>
       </c>
       <c r="E22" t="n">
-        <v>1.947</v>
+        <v>1.565</v>
       </c>
       <c r="F22" t="n">
-        <v>18.81</v>
+        <v>10.113</v>
       </c>
       <c r="G22" t="n">
-        <v>46.507</v>
+        <v>25.913</v>
       </c>
       <c r="H22" t="n">
-        <v>1.113</v>
+        <v>0.666</v>
       </c>
       <c r="I22" t="n">
-        <v>3.002</v>
+        <v>1.729</v>
       </c>
       <c r="J22" t="inlineStr"/>
     </row>
@@ -1224,29 +1212,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>liq-amph</t>
+          <t>liq-ilm</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>157</v>
+        <v>74</v>
       </c>
       <c r="D23" t="n">
-        <v>0.592</v>
+        <v>0.771</v>
       </c>
       <c r="E23" t="n">
-        <v>1.565</v>
+        <v>1.996</v>
       </c>
       <c r="F23" t="n">
-        <v>10.113</v>
+        <v>10.945</v>
       </c>
       <c r="G23" t="n">
-        <v>25.913</v>
+        <v>28.63</v>
       </c>
       <c r="H23" t="n">
-        <v>0.666</v>
+        <v>0.833</v>
       </c>
       <c r="I23" t="n">
-        <v>1.729</v>
+        <v>2.219</v>
       </c>
       <c r="J23" t="inlineStr"/>
     </row>
@@ -1292,31 +1280,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>cpx-sp</t>
+          <t>liq-sp</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>139</v>
+        <v>206</v>
       </c>
       <c r="D25" t="n">
-        <v>0.66</v>
+        <v>0.672</v>
       </c>
       <c r="E25" t="n">
-        <v>1.805</v>
+        <v>1.638</v>
       </c>
       <c r="F25" t="n">
-        <v>19.508</v>
+        <v>19.241</v>
       </c>
       <c r="G25" t="n">
-        <v>50.482</v>
+        <v>50.078</v>
       </c>
       <c r="H25" t="n">
-        <v>0.804</v>
+        <v>1.091</v>
       </c>
       <c r="I25" t="n">
-        <v>2.113</v>
-      </c>
-      <c r="J25" t="inlineStr"/>
+        <v>2.833</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1326,29 +1318,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>plg-mag</t>
+          <t>liq-grt</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="D26" t="n">
-        <v>0.643</v>
+        <v>0.906</v>
       </c>
       <c r="E26" t="n">
-        <v>1.684</v>
+        <v>2.29</v>
       </c>
       <c r="F26" t="n">
-        <v>19.768</v>
+        <v>22.765</v>
       </c>
       <c r="G26" t="n">
-        <v>49.82</v>
+        <v>56.793</v>
       </c>
       <c r="H26" t="n">
-        <v>1.16</v>
+        <v>0.897</v>
       </c>
       <c r="I26" t="n">
-        <v>3.03</v>
+        <v>2.329</v>
       </c>
       <c r="J26" t="inlineStr"/>
     </row>
@@ -1360,29 +1352,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>cpx-mag</t>
+          <t>ol-opx</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="D27" t="n">
-        <v>0.657</v>
+        <v>0.554</v>
       </c>
       <c r="E27" t="n">
-        <v>1.764</v>
+        <v>1.415</v>
       </c>
       <c r="F27" t="n">
-        <v>14.803</v>
+        <v>22.495</v>
       </c>
       <c r="G27" t="n">
-        <v>37.897</v>
+        <v>59.49</v>
       </c>
       <c r="H27" t="n">
-        <v>0.533</v>
+        <v>0.98</v>
       </c>
       <c r="I27" t="n">
-        <v>1.383</v>
+        <v>2.432</v>
       </c>
       <c r="J27" t="inlineStr"/>
     </row>
@@ -1394,29 +1386,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ol-sp</t>
+          <t>ol-amph</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>122</v>
+        <v>36</v>
       </c>
       <c r="D28" t="n">
-        <v>0.727</v>
+        <v>0.627</v>
       </c>
       <c r="E28" t="n">
-        <v>1.875</v>
+        <v>1.476</v>
       </c>
       <c r="F28" t="n">
-        <v>23.312</v>
+        <v>11.148</v>
       </c>
       <c r="G28" t="n">
-        <v>59.713</v>
+        <v>28.488</v>
       </c>
       <c r="H28" t="n">
-        <v>1.106</v>
+        <v>0.721</v>
       </c>
       <c r="I28" t="n">
-        <v>2.891</v>
+        <v>1.652</v>
       </c>
       <c r="J28" t="inlineStr"/>
     </row>
@@ -1428,29 +1420,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>plg-amph</t>
+          <t>ol-ilm</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>121</v>
+        <v>13</v>
       </c>
       <c r="D29" t="n">
-        <v>0.608</v>
+        <v>0.715</v>
       </c>
       <c r="E29" t="n">
-        <v>1.56</v>
+        <v>1.555</v>
       </c>
       <c r="F29" t="n">
-        <v>12.261</v>
+        <v>15.852</v>
       </c>
       <c r="G29" t="n">
-        <v>31.763</v>
+        <v>39.332</v>
       </c>
       <c r="H29" t="n">
-        <v>0.59</v>
+        <v>0.334</v>
       </c>
       <c r="I29" t="n">
-        <v>1.523</v>
+        <v>0.861</v>
       </c>
       <c r="J29" t="inlineStr"/>
     </row>
@@ -1462,29 +1454,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>plg-sp</t>
+          <t>ol-mag</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="D30" t="n">
-        <v>0.652</v>
+        <v>0.465</v>
       </c>
       <c r="E30" t="n">
-        <v>1.62</v>
+        <v>1.187</v>
       </c>
       <c r="F30" t="n">
-        <v>18.73</v>
+        <v>12.841</v>
       </c>
       <c r="G30" t="n">
-        <v>49.51</v>
+        <v>33.587</v>
       </c>
       <c r="H30" t="n">
-        <v>0.774</v>
+        <v>1.126</v>
       </c>
       <c r="I30" t="n">
-        <v>2.051</v>
+        <v>2.802</v>
       </c>
       <c r="J30" t="inlineStr"/>
     </row>
@@ -1496,29 +1488,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ol-opx</t>
+          <t>ol-sp</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="D31" t="n">
-        <v>0.554</v>
+        <v>0.727</v>
       </c>
       <c r="E31" t="n">
-        <v>1.415</v>
+        <v>1.875</v>
       </c>
       <c r="F31" t="n">
-        <v>22.495</v>
+        <v>23.312</v>
       </c>
       <c r="G31" t="n">
-        <v>59.49</v>
+        <v>59.713</v>
       </c>
       <c r="H31" t="n">
-        <v>0.98</v>
+        <v>1.106</v>
       </c>
       <c r="I31" t="n">
-        <v>2.432</v>
+        <v>2.891</v>
       </c>
       <c r="J31" t="inlineStr"/>
     </row>
@@ -1530,30 +1522,18 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>cpx-amph</t>
+          <t>ol-grt</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>75</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.5679999999999999</v>
-      </c>
-      <c r="E32" t="n">
-        <v>1.459</v>
-      </c>
-      <c r="F32" t="n">
-        <v>10.887</v>
-      </c>
-      <c r="G32" t="n">
-        <v>27.953</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.618</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1.635</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1564,31 +1544,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ilm</t>
+          <t>cpx-opx</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>74</v>
+        <v>215</v>
       </c>
       <c r="D33" t="n">
-        <v>1.081</v>
+        <v>0.709</v>
       </c>
       <c r="E33" t="n">
-        <v>2.883</v>
+        <v>1.843</v>
       </c>
       <c r="F33" t="n">
-        <v>28.393</v>
+        <v>20.283</v>
       </c>
       <c r="G33" t="n">
-        <v>74.161</v>
+        <v>52.261</v>
       </c>
       <c r="H33" t="n">
-        <v>0.857</v>
+        <v>0.835</v>
       </c>
       <c r="I33" t="n">
-        <v>2.285</v>
-      </c>
-      <c r="J33" t="inlineStr"/>
+        <v>2.111</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1598,29 +1582,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>liq-ilm</t>
+          <t>cpx-amph</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D34" t="n">
-        <v>0.771</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>1.996</v>
+        <v>1.459</v>
       </c>
       <c r="F34" t="n">
-        <v>10.945</v>
+        <v>10.887</v>
       </c>
       <c r="G34" t="n">
-        <v>28.63</v>
+        <v>27.953</v>
       </c>
       <c r="H34" t="n">
-        <v>0.833</v>
+        <v>0.618</v>
       </c>
       <c r="I34" t="n">
-        <v>2.219</v>
+        <v>1.635</v>
       </c>
       <c r="J34" t="inlineStr"/>
     </row>
@@ -1632,29 +1616,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>opx-sp</t>
+          <t>cpx-ilm</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="D35" t="n">
-        <v>0.727</v>
+        <v>0.795</v>
       </c>
       <c r="E35" t="n">
-        <v>1.917</v>
+        <v>2.133</v>
       </c>
       <c r="F35" t="n">
-        <v>23.5</v>
+        <v>18.779</v>
       </c>
       <c r="G35" t="n">
-        <v>61.787</v>
+        <v>49.818</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7</v>
+        <v>0.789</v>
       </c>
       <c r="I35" t="n">
-        <v>1.719</v>
+        <v>2.043</v>
       </c>
       <c r="J35" t="inlineStr"/>
     </row>
@@ -1666,29 +1650,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>plg-ilm</t>
+          <t>cpx-mag</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="D36" t="n">
-        <v>0.803</v>
+        <v>0.657</v>
       </c>
       <c r="E36" t="n">
-        <v>2.119</v>
+        <v>1.764</v>
       </c>
       <c r="F36" t="n">
-        <v>23.059</v>
+        <v>14.803</v>
       </c>
       <c r="G36" t="n">
-        <v>59.042</v>
+        <v>37.897</v>
       </c>
       <c r="H36" t="n">
-        <v>0.928</v>
+        <v>0.533</v>
       </c>
       <c r="I36" t="n">
-        <v>2.451</v>
+        <v>1.383</v>
       </c>
       <c r="J36" t="inlineStr"/>
     </row>
@@ -1700,29 +1684,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ol-mag</t>
+          <t>cpx-sp</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>66</v>
+        <v>139</v>
       </c>
       <c r="D37" t="n">
-        <v>0.465</v>
+        <v>0.66</v>
       </c>
       <c r="E37" t="n">
-        <v>1.187</v>
+        <v>1.805</v>
       </c>
       <c r="F37" t="n">
-        <v>12.841</v>
+        <v>19.508</v>
       </c>
       <c r="G37" t="n">
-        <v>33.587</v>
+        <v>50.482</v>
       </c>
       <c r="H37" t="n">
-        <v>1.126</v>
+        <v>0.804</v>
       </c>
       <c r="I37" t="n">
-        <v>2.802</v>
+        <v>2.113</v>
       </c>
       <c r="J37" t="inlineStr"/>
     </row>
@@ -1734,29 +1718,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>opx-mag</t>
+          <t>cpx-grt</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D38" t="n">
-        <v>0.755</v>
+        <v>0.77</v>
       </c>
       <c r="E38" t="n">
-        <v>1.983</v>
+        <v>2.059</v>
       </c>
       <c r="F38" t="n">
-        <v>18.617</v>
+        <v>26.191</v>
       </c>
       <c r="G38" t="n">
-        <v>45.956</v>
+        <v>65.893</v>
       </c>
       <c r="H38" t="n">
-        <v>0.621</v>
+        <v>1.117</v>
       </c>
       <c r="I38" t="n">
-        <v>1.601</v>
+        <v>2.931</v>
       </c>
       <c r="J38" t="inlineStr"/>
     </row>
@@ -1768,31 +1752,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>opx-amph</t>
+          <t>plg-opx</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>59</v>
+        <v>208</v>
       </c>
       <c r="D39" t="n">
-        <v>0.645</v>
+        <v>0.721</v>
       </c>
       <c r="E39" t="n">
-        <v>1.582</v>
+        <v>1.94</v>
       </c>
       <c r="F39" t="n">
-        <v>11.687</v>
+        <v>24.794</v>
       </c>
       <c r="G39" t="n">
-        <v>29.024</v>
+        <v>65.69199999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>0.547</v>
+        <v>0.799</v>
       </c>
       <c r="I39" t="n">
-        <v>1.383</v>
-      </c>
-      <c r="J39" t="inlineStr"/>
+        <v>1.997</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1802,29 +1790,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>amph-mag</t>
+          <t>plg-amph</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="D40" t="n">
-        <v>0.611</v>
+        <v>0.608</v>
       </c>
       <c r="E40" t="n">
-        <v>1.563</v>
+        <v>1.56</v>
       </c>
       <c r="F40" t="n">
-        <v>13.628</v>
+        <v>12.261</v>
       </c>
       <c r="G40" t="n">
-        <v>29.764</v>
+        <v>31.763</v>
       </c>
       <c r="H40" t="n">
-        <v>0.761</v>
+        <v>0.59</v>
       </c>
       <c r="I40" t="n">
-        <v>1.916</v>
+        <v>1.523</v>
       </c>
       <c r="J40" t="inlineStr"/>
     </row>
@@ -1836,29 +1824,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>cpx-ilm</t>
+          <t>plg-ilm</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="D41" t="n">
-        <v>0.795</v>
+        <v>0.803</v>
       </c>
       <c r="E41" t="n">
-        <v>2.133</v>
+        <v>2.119</v>
       </c>
       <c r="F41" t="n">
-        <v>18.779</v>
+        <v>23.059</v>
       </c>
       <c r="G41" t="n">
-        <v>49.818</v>
+        <v>59.042</v>
       </c>
       <c r="H41" t="n">
-        <v>0.789</v>
+        <v>0.928</v>
       </c>
       <c r="I41" t="n">
-        <v>2.043</v>
+        <v>2.451</v>
       </c>
       <c r="J41" t="inlineStr"/>
     </row>
@@ -1870,29 +1858,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>grt</t>
+          <t>plg-mag</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="D42" t="n">
-        <v>0.973</v>
+        <v>0.643</v>
       </c>
       <c r="E42" t="n">
-        <v>2.384</v>
+        <v>1.684</v>
       </c>
       <c r="F42" t="n">
-        <v>28.818</v>
+        <v>19.768</v>
       </c>
       <c r="G42" t="n">
-        <v>68.611</v>
+        <v>49.82</v>
       </c>
       <c r="H42" t="n">
-        <v>0.876</v>
+        <v>1.16</v>
       </c>
       <c r="I42" t="n">
-        <v>2.11</v>
+        <v>3.03</v>
       </c>
       <c r="J42" t="inlineStr"/>
     </row>
@@ -1904,29 +1892,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>liq-grt</t>
+          <t>plg-sp</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="D43" t="n">
-        <v>0.906</v>
+        <v>0.652</v>
       </c>
       <c r="E43" t="n">
-        <v>2.29</v>
+        <v>1.62</v>
       </c>
       <c r="F43" t="n">
-        <v>22.765</v>
+        <v>18.73</v>
       </c>
       <c r="G43" t="n">
-        <v>56.793</v>
+        <v>49.51</v>
       </c>
       <c r="H43" t="n">
-        <v>0.897</v>
+        <v>0.774</v>
       </c>
       <c r="I43" t="n">
-        <v>2.329</v>
+        <v>2.051</v>
       </c>
       <c r="J43" t="inlineStr"/>
     </row>
@@ -1938,29 +1926,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>amph-ilm</t>
+          <t>plg-grt</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D44" t="n">
-        <v>0.618</v>
+        <v>0.799</v>
       </c>
       <c r="E44" t="n">
-        <v>1.652</v>
+        <v>2.029</v>
       </c>
       <c r="F44" t="n">
-        <v>11.255</v>
+        <v>23.164</v>
       </c>
       <c r="G44" t="n">
-        <v>28.259</v>
+        <v>56.307</v>
       </c>
       <c r="H44" t="n">
-        <v>0.596</v>
+        <v>0.541</v>
       </c>
       <c r="I44" t="n">
-        <v>1.408</v>
+        <v>1.351</v>
       </c>
       <c r="J44" t="inlineStr"/>
     </row>
@@ -1972,29 +1960,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ol-amph</t>
+          <t>opx-amph</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D45" t="n">
-        <v>0.627</v>
+        <v>0.645</v>
       </c>
       <c r="E45" t="n">
-        <v>1.476</v>
+        <v>1.582</v>
       </c>
       <c r="F45" t="n">
-        <v>11.148</v>
+        <v>11.687</v>
       </c>
       <c r="G45" t="n">
-        <v>28.488</v>
+        <v>29.024</v>
       </c>
       <c r="H45" t="n">
-        <v>0.721</v>
+        <v>0.547</v>
       </c>
       <c r="I45" t="n">
-        <v>1.652</v>
+        <v>1.383</v>
       </c>
       <c r="J45" t="inlineStr"/>
     </row>
@@ -2040,29 +2028,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ilm-mag</t>
+          <t>opx-mag</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="D47" t="n">
-        <v>0.67</v>
+        <v>0.755</v>
       </c>
       <c r="E47" t="n">
-        <v>1.809</v>
+        <v>1.983</v>
       </c>
       <c r="F47" t="n">
-        <v>18.963</v>
+        <v>18.617</v>
       </c>
       <c r="G47" t="n">
-        <v>44.636</v>
+        <v>45.956</v>
       </c>
       <c r="H47" t="n">
-        <v>0.511</v>
+        <v>0.621</v>
       </c>
       <c r="I47" t="n">
-        <v>1.161</v>
+        <v>1.601</v>
       </c>
       <c r="J47" t="inlineStr"/>
     </row>
@@ -2074,29 +2062,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>amph-sp</t>
+          <t>opx-sp</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="D48" t="n">
-        <v>0.873</v>
+        <v>0.727</v>
       </c>
       <c r="E48" t="n">
-        <v>2.029</v>
+        <v>1.917</v>
       </c>
       <c r="F48" t="n">
-        <v>17.376</v>
+        <v>23.5</v>
       </c>
       <c r="G48" t="n">
-        <v>42.116</v>
+        <v>61.787</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="I48" t="n">
-        <v>2.349</v>
+        <v>1.719</v>
       </c>
       <c r="J48" t="inlineStr"/>
     </row>
@@ -2108,29 +2096,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>plg-grt</t>
+          <t>opx-grt</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D49" t="n">
-        <v>0.799</v>
+        <v>1.324</v>
       </c>
       <c r="E49" t="n">
-        <v>2.029</v>
+        <v>3.519</v>
       </c>
       <c r="F49" t="n">
-        <v>23.164</v>
+        <v>44.946</v>
       </c>
       <c r="G49" t="n">
-        <v>56.307</v>
+        <v>119.855</v>
       </c>
       <c r="H49" t="n">
-        <v>0.541</v>
+        <v>0.624</v>
       </c>
       <c r="I49" t="n">
-        <v>1.351</v>
+        <v>1.687</v>
       </c>
       <c r="J49" t="inlineStr"/>
     </row>
@@ -2142,29 +2130,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>cpx-grt</t>
+          <t>amph-ilm</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D50" t="n">
-        <v>0.77</v>
+        <v>0.618</v>
       </c>
       <c r="E50" t="n">
-        <v>2.059</v>
+        <v>1.652</v>
       </c>
       <c r="F50" t="n">
-        <v>26.191</v>
+        <v>11.255</v>
       </c>
       <c r="G50" t="n">
-        <v>65.893</v>
+        <v>28.259</v>
       </c>
       <c r="H50" t="n">
-        <v>1.117</v>
+        <v>0.596</v>
       </c>
       <c r="I50" t="n">
-        <v>2.931</v>
+        <v>1.408</v>
       </c>
       <c r="J50" t="inlineStr"/>
     </row>
@@ -2176,29 +2164,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>amph-grt</t>
+          <t>amph-mag</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D51" t="n">
-        <v>0.699</v>
+        <v>0.611</v>
       </c>
       <c r="E51" t="n">
-        <v>1.747</v>
+        <v>1.563</v>
       </c>
       <c r="F51" t="n">
-        <v>18.219</v>
+        <v>13.628</v>
       </c>
       <c r="G51" t="n">
-        <v>43.985</v>
+        <v>29.764</v>
       </c>
       <c r="H51" t="n">
-        <v>0.492</v>
+        <v>0.761</v>
       </c>
       <c r="I51" t="n">
-        <v>1.297</v>
+        <v>1.916</v>
       </c>
       <c r="J51" t="inlineStr"/>
     </row>
@@ -2210,29 +2198,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ilm-grt</t>
+          <t>amph-sp</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D52" t="n">
-        <v>1.172</v>
+        <v>0.873</v>
       </c>
       <c r="E52" t="n">
-        <v>2.539</v>
+        <v>2.029</v>
       </c>
       <c r="F52" t="n">
-        <v>27.291</v>
+        <v>17.376</v>
       </c>
       <c r="G52" t="n">
-        <v>64.23699999999999</v>
+        <v>42.116</v>
       </c>
       <c r="H52" t="n">
-        <v>0.315</v>
+        <v>0.9</v>
       </c>
       <c r="I52" t="n">
-        <v>0.681</v>
+        <v>2.349</v>
       </c>
       <c r="J52" t="inlineStr"/>
     </row>
@@ -2244,29 +2232,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ol-ilm</t>
+          <t>amph-grt</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D53" t="n">
-        <v>0.715</v>
+        <v>0.699</v>
       </c>
       <c r="E53" t="n">
-        <v>1.555</v>
+        <v>1.747</v>
       </c>
       <c r="F53" t="n">
-        <v>15.852</v>
+        <v>18.219</v>
       </c>
       <c r="G53" t="n">
-        <v>39.332</v>
+        <v>43.985</v>
       </c>
       <c r="H53" t="n">
-        <v>0.334</v>
+        <v>0.492</v>
       </c>
       <c r="I53" t="n">
-        <v>0.861</v>
+        <v>1.297</v>
       </c>
       <c r="J53" t="inlineStr"/>
     </row>
@@ -2278,29 +2266,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ilm-sp</t>
+          <t>ilm-mag</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="D54" t="n">
-        <v>1.428</v>
+        <v>0.67</v>
       </c>
       <c r="E54" t="n">
-        <v>3.932</v>
+        <v>1.809</v>
       </c>
       <c r="F54" t="n">
-        <v>29.7</v>
+        <v>18.963</v>
       </c>
       <c r="G54" t="n">
-        <v>67.15600000000001</v>
+        <v>44.636</v>
       </c>
       <c r="H54" t="n">
-        <v>1.159</v>
+        <v>0.511</v>
       </c>
       <c r="I54" t="n">
-        <v>3.174</v>
+        <v>1.161</v>
       </c>
       <c r="J54" t="inlineStr"/>
     </row>
@@ -2312,29 +2300,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>opx-grt</t>
+          <t>ilm-sp</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D55" t="n">
-        <v>1.324</v>
+        <v>1.428</v>
       </c>
       <c r="E55" t="n">
-        <v>3.519</v>
+        <v>3.932</v>
       </c>
       <c r="F55" t="n">
-        <v>44.946</v>
+        <v>29.7</v>
       </c>
       <c r="G55" t="n">
-        <v>119.855</v>
+        <v>67.15600000000001</v>
       </c>
       <c r="H55" t="n">
-        <v>0.624</v>
+        <v>1.159</v>
       </c>
       <c r="I55" t="n">
-        <v>1.687</v>
+        <v>3.174</v>
       </c>
       <c r="J55" t="inlineStr"/>
     </row>
@@ -2346,18 +2334,30 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>sp-grt</t>
+          <t>ilm-grt</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.172</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2.539</v>
+      </c>
+      <c r="F56" t="n">
+        <v>27.291</v>
+      </c>
+      <c r="G56" t="n">
+        <v>64.23699999999999</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.681</v>
+      </c>
       <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ol-grt</t>
+          <t>mag-sp</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>mag-sp</t>
+          <t>mag-grt</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -2412,11 +2412,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>mag-grt</t>
+          <t>sp-grt</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
